--- a/P1-FrailejonDetection/trials-data/suggest-units1-dorpout1-activationl1_6.xlsx
+++ b/P1-FrailejonDetection/trials-data/suggest-units1-dorpout1-activationl1_6.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\dev-env\workSpace\topicosAvanzadosAnalitica\P1-FrailejonDetection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\dev-env\workSpace\topicosAvanzadosAnalitica\P1-FrailejonDetection\trials-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA3267B-6430-4165-9016-C353AF9FC55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CFF95F-E4E5-4209-85B2-265FD3D7027C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,6 +103,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -131,20 +145,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63D95CC6-6828-4FA2-8713-225085DF94D9}" name="Table1" displayName="Table1" ref="A1:F94" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63D95CC6-6828-4FA2-8713-225085DF94D9}" name="Table1" displayName="Table1" ref="A1:F94" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:F94" xr:uid="{63D95CC6-6828-4FA2-8713-225085DF94D9}">
     <filterColumn colId="0">
       <customFilters>
@@ -509,10 +509,10 @@
         <v>76</v>
       </c>
       <c r="E2">
-        <v>0.28195796475963891</v>
+        <v>0.28195796475963902</v>
       </c>
       <c r="F2">
-        <v>2.745518225857252E-5</v>
+        <v>2.7455182258572499E-5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
